--- a/data/Data Final.xlsx
+++ b/data/Data Final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56183906-8D35-47F4-86E6-7BFD64019810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5EB68C-DBB4-43A6-BD31-29FE947EC50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="2023" sheetId="4" r:id="rId4"/>
     <sheet name="2024" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -595,7 +608,7 @@
         <v>7.37</v>
       </c>
       <c r="M2" s="7">
-        <v>60.7</v>
+        <v>60.67</v>
       </c>
       <c r="N2" s="1">
         <v>0.30599999999999999</v>
@@ -642,7 +655,7 @@
         <v>10.79</v>
       </c>
       <c r="M3" s="7">
-        <v>63.81</v>
+        <v>63.980000000000004</v>
       </c>
       <c r="N3" s="1">
         <v>0.42699999999999999</v>
@@ -689,7 +702,7 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="M4" s="7">
-        <v>61.98</v>
+        <v>62.125</v>
       </c>
       <c r="N4" s="1">
         <v>0.36299999999999999</v>
@@ -736,7 +749,7 @@
         <v>10.97</v>
       </c>
       <c r="M5" s="7">
-        <v>63.73</v>
+        <v>63.975000000000001</v>
       </c>
       <c r="N5" s="1">
         <v>0.39</v>
@@ -783,7 +796,7 @@
         <v>12.27</v>
       </c>
       <c r="M6" s="7">
-        <v>64.37</v>
+        <v>64.39500000000001</v>
       </c>
       <c r="N6" s="1">
         <v>0.38</v>
@@ -830,7 +843,7 @@
         <v>11.79</v>
       </c>
       <c r="M7" s="7">
-        <v>65.97</v>
+        <v>66.325000000000003</v>
       </c>
       <c r="N7" s="1">
         <v>0.41299999999999998</v>
@@ -877,7 +890,7 @@
         <v>14.29</v>
       </c>
       <c r="M8" s="7">
-        <v>62.65</v>
+        <v>62.185000000000002</v>
       </c>
       <c r="N8" s="1">
         <v>0.38100000000000001</v>
@@ -924,7 +937,7 @@
         <v>9.6</v>
       </c>
       <c r="M9" s="7">
-        <v>61.56</v>
+        <v>61.325000000000003</v>
       </c>
       <c r="N9" s="1">
         <v>0.33400000000000002</v>
@@ -971,7 +984,7 @@
         <v>11.05</v>
       </c>
       <c r="M10" s="7">
-        <v>69.260000000000005</v>
+        <v>68.69</v>
       </c>
       <c r="N10" s="1">
         <v>0.35</v>
@@ -1018,7 +1031,7 @@
         <v>8.58</v>
       </c>
       <c r="M11" s="7">
-        <v>62.2</v>
+        <v>61.98</v>
       </c>
       <c r="N11" s="1">
         <v>0.41399999999999998</v>
@@ -1065,7 +1078,7 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="M12" s="7">
-        <v>61.11</v>
+        <v>61.055</v>
       </c>
       <c r="N12" s="1">
         <v>0.35199999999999998</v>
@@ -1112,7 +1125,7 @@
         <v>7.12</v>
       </c>
       <c r="M13" s="7">
-        <v>69.540000000000006</v>
+        <v>69.83</v>
       </c>
       <c r="N13" s="1">
         <v>0.34300000000000003</v>
@@ -1159,7 +1172,7 @@
         <v>5.66</v>
       </c>
       <c r="M14" s="7">
-        <v>71.41</v>
+        <v>71.745000000000005</v>
       </c>
       <c r="N14" s="1">
         <v>0.33600000000000002</v>
@@ -1206,7 +1219,7 @@
         <v>11.22</v>
       </c>
       <c r="M15" s="7">
-        <v>61.98</v>
+        <v>62.045000000000002</v>
       </c>
       <c r="N15" s="1">
         <v>0.36099999999999999</v>
@@ -1253,7 +1266,7 @@
         <v>11.52</v>
       </c>
       <c r="M16" s="7">
-        <v>63.79</v>
+        <v>63.42</v>
       </c>
       <c r="N16" s="1">
         <v>0.33800000000000002</v>
@@ -1300,7 +1313,7 @@
         <v>5.84</v>
       </c>
       <c r="M17" s="7">
-        <v>69.66</v>
+        <v>69.805000000000007</v>
       </c>
       <c r="N17" s="1">
         <v>0.33600000000000002</v>
@@ -1347,7 +1360,7 @@
         <v>9.89</v>
       </c>
       <c r="M18" s="7">
-        <v>68.959999999999994</v>
+        <v>69.13</v>
       </c>
       <c r="N18" s="1">
         <v>0.38400000000000001</v>
@@ -1394,7 +1407,7 @@
         <v>9.2100000000000009</v>
       </c>
       <c r="M19" s="7">
-        <v>69.53</v>
+        <v>69.039999999999992</v>
       </c>
       <c r="N19" s="1">
         <v>0.31900000000000001</v>
@@ -1441,7 +1454,7 @@
         <v>9.48</v>
       </c>
       <c r="M20" s="7">
-        <v>66.7</v>
+        <v>66.62</v>
       </c>
       <c r="N20" s="1">
         <v>0.35</v>
@@ -1488,7 +1501,7 @@
         <v>11.07</v>
       </c>
       <c r="M21" s="7">
-        <v>60.91</v>
+        <v>60.555</v>
       </c>
       <c r="N21" s="1">
         <v>0.41399999999999998</v>
@@ -1535,7 +1548,7 @@
         <v>11.52</v>
       </c>
       <c r="M22" s="7">
-        <v>64.900000000000006</v>
+        <v>64.38</v>
       </c>
       <c r="N22" s="1">
         <v>0.32700000000000001</v>
@@ -1582,7 +1595,7 @@
         <v>11.54</v>
       </c>
       <c r="M23" s="7">
-        <v>64.23</v>
+        <v>63.879999999999995</v>
       </c>
       <c r="N23" s="1">
         <v>0.372</v>
@@ -1629,7 +1642,7 @@
         <v>12.25</v>
       </c>
       <c r="M24" s="7">
-        <v>59.91</v>
+        <v>59.6</v>
       </c>
       <c r="N24" s="1">
         <v>0.376</v>
@@ -1676,7 +1689,7 @@
         <v>5.08</v>
       </c>
       <c r="M25" s="7">
-        <v>76.790000000000006</v>
+        <v>76.965000000000003</v>
       </c>
       <c r="N25" s="1">
         <v>0.33500000000000002</v>
@@ -1723,7 +1736,7 @@
         <v>12.68</v>
       </c>
       <c r="M26" s="7">
-        <v>60.81</v>
+        <v>60.61</v>
       </c>
       <c r="N26" s="1">
         <v>0.41199999999999998</v>
@@ -1770,7 +1783,7 @@
         <v>12.17</v>
       </c>
       <c r="M27" s="7">
-        <v>55.74</v>
+        <v>55.57</v>
       </c>
       <c r="N27" s="1">
         <v>0.39700000000000002</v>
@@ -1817,7 +1830,7 @@
         <v>11.19</v>
       </c>
       <c r="M28" s="7">
-        <v>64.709999999999994</v>
+        <v>64.614999999999995</v>
       </c>
       <c r="N28" s="1">
         <v>0.40200000000000002</v>
@@ -1864,7 +1877,7 @@
         <v>10.97</v>
       </c>
       <c r="M29" s="7">
-        <v>63.76</v>
+        <v>63.865000000000002</v>
       </c>
       <c r="N29" s="1">
         <v>0.42099999999999999</v>
@@ -1911,7 +1924,7 @@
         <v>10.68</v>
       </c>
       <c r="M30" s="7">
-        <v>64.739999999999995</v>
+        <v>64.674999999999997</v>
       </c>
       <c r="N30" s="1">
         <v>0.35199999999999998</v>
@@ -1958,7 +1971,7 @@
         <v>9.8699999999999992</v>
       </c>
       <c r="M31" s="7">
-        <v>63.96</v>
+        <v>63.91</v>
       </c>
       <c r="N31" s="1">
         <v>0.34399999999999997</v>
@@ -2005,7 +2018,7 @@
         <v>13.3</v>
       </c>
       <c r="M32" s="7">
-        <v>62.67</v>
+        <v>62.604999999999997</v>
       </c>
       <c r="N32" s="1">
         <v>0.38</v>
@@ -2052,7 +2065,7 @@
         <v>7.99</v>
       </c>
       <c r="M33" s="7">
-        <v>66.540000000000006</v>
+        <v>66.53</v>
       </c>
       <c r="N33" s="1">
         <v>0.36599999999999999</v>
@@ -2099,7 +2112,7 @@
         <v>6.73</v>
       </c>
       <c r="M34" s="7">
-        <v>67.349999999999994</v>
+        <v>67.614999999999995</v>
       </c>
       <c r="N34" s="1">
         <v>0.312</v>
@@ -2146,7 +2159,7 @@
         <v>9.15</v>
       </c>
       <c r="M35" s="7">
-        <v>60.28</v>
+        <v>59.914999999999999</v>
       </c>
       <c r="N35" s="1">
         <v>0.30499999999999999</v>
@@ -2193,7 +2206,7 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="M36" s="7">
-        <v>69.97</v>
+        <v>69.58</v>
       </c>
       <c r="N36" s="1">
         <v>0.314</v>
@@ -2240,7 +2253,7 @@
         <v>13.06</v>
       </c>
       <c r="M37" s="7">
-        <v>65.430000000000007</v>
+        <v>65.02000000000001</v>
       </c>
       <c r="N37" s="1">
         <v>0.28499999999999998</v>
@@ -2287,7 +2300,7 @@
         <v>12.22</v>
       </c>
       <c r="M38" s="7">
-        <v>63.46</v>
+        <v>63.29</v>
       </c>
       <c r="N38" s="1">
         <v>0.30299999999999999</v>
@@ -2313,7 +2326,7 @@
         <v>5.22</v>
       </c>
       <c r="F39" s="6">
-        <v>102415.7</v>
+        <v>102415.67999999999</v>
       </c>
       <c r="G39" s="6">
         <v>10.69</v>
@@ -2334,7 +2347,7 @@
         <v>8.6300000000000008</v>
       </c>
       <c r="M39" s="7">
-        <v>64.97</v>
+        <v>64.62</v>
       </c>
       <c r="N39" s="1">
         <v>0.33900000000000002</v>
@@ -2381,7 +2394,7 @@
         <v>12.69</v>
       </c>
       <c r="M40" s="7">
-        <v>61.83</v>
+        <v>61.379999999999995</v>
       </c>
       <c r="N40" s="1">
         <v>0.373</v>
@@ -2428,7 +2441,7 @@
         <v>9.26</v>
       </c>
       <c r="M41" s="7">
-        <v>63.79</v>
+        <v>63.325000000000003</v>
       </c>
       <c r="N41" s="1">
         <v>0.35199999999999998</v>
@@ -2475,7 +2488,7 @@
         <v>8.48</v>
       </c>
       <c r="M42" s="7">
-        <v>62.49</v>
+        <v>62.424999999999997</v>
       </c>
       <c r="N42" s="1">
         <v>0.36799999999999999</v>
@@ -2584,7 +2597,7 @@
         <v>15.06</v>
       </c>
       <c r="F2" s="6">
-        <v>3648.88</v>
+        <v>3648.8</v>
       </c>
       <c r="G2" s="6">
         <v>8.81</v>
@@ -2605,7 +2618,7 @@
         <v>8.58</v>
       </c>
       <c r="M2" s="7">
-        <v>65.45</v>
+        <v>65.454999999999998</v>
       </c>
       <c r="N2" s="1">
         <v>0.245</v>
@@ -2631,7 +2644,7 @@
         <v>3.56</v>
       </c>
       <c r="F3" s="6">
-        <v>429278</v>
+        <v>429259.25</v>
       </c>
       <c r="G3" s="6">
         <v>11.64</v>
@@ -2652,7 +2665,7 @@
         <v>7.33</v>
       </c>
       <c r="M3" s="7">
-        <v>61.44</v>
+        <v>61.64</v>
       </c>
       <c r="N3" s="1">
         <v>0.38300000000000001</v>
@@ -2678,7 +2691,7 @@
         <v>4.28</v>
       </c>
       <c r="F4" s="6">
-        <v>313816.5</v>
+        <v>313808.7</v>
       </c>
       <c r="G4" s="6">
         <v>11.67</v>
@@ -2699,7 +2712,7 @@
         <v>8.23</v>
       </c>
       <c r="M4" s="7">
-        <v>60.85</v>
+        <v>61.03</v>
       </c>
       <c r="N4" s="1">
         <v>0.374</v>
@@ -2725,7 +2738,7 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="F5" s="6">
-        <v>460024.3</v>
+        <v>459971.27</v>
       </c>
       <c r="G5" s="6">
         <v>11.39</v>
@@ -2746,7 +2759,7 @@
         <v>7.75</v>
       </c>
       <c r="M5" s="7">
-        <v>63.17</v>
+        <v>63.395000000000003</v>
       </c>
       <c r="N5" s="1">
         <v>0.39700000000000002</v>
@@ -2772,7 +2785,7 @@
         <v>4.3099999999999996</v>
       </c>
       <c r="F6" s="6">
-        <v>327613.09999999998</v>
+        <v>327599.15999999997</v>
       </c>
       <c r="G6" s="6">
         <v>10.78</v>
@@ -2793,7 +2806,7 @@
         <v>9.06</v>
       </c>
       <c r="M6" s="7">
-        <v>63.21</v>
+        <v>63.29</v>
       </c>
       <c r="N6" s="1">
         <v>0.36599999999999999</v>
@@ -2819,7 +2832,7 @@
         <v>7.24</v>
       </c>
       <c r="F7" s="6">
-        <v>330883.90000000002</v>
+        <v>330890.18</v>
       </c>
       <c r="G7" s="6">
         <v>10.81</v>
@@ -2840,7 +2853,7 @@
         <v>9.84</v>
       </c>
       <c r="M7" s="7">
-        <v>65.790000000000006</v>
+        <v>66.155000000000001</v>
       </c>
       <c r="N7" s="1">
         <v>0.51500000000000001</v>
@@ -2866,7 +2879,7 @@
         <v>8.1300000000000008</v>
       </c>
       <c r="F8" s="6">
-        <v>159589.6</v>
+        <v>159589.54999999999</v>
       </c>
       <c r="G8" s="6">
         <v>8.31</v>
@@ -2887,7 +2900,7 @@
         <v>12.22</v>
       </c>
       <c r="M8" s="7">
-        <v>62.55</v>
+        <v>62.08</v>
       </c>
       <c r="N8" s="1">
         <v>0.39600000000000002</v>
@@ -2934,7 +2947,7 @@
         <v>9.51</v>
       </c>
       <c r="M9" s="7">
-        <v>64.930000000000007</v>
+        <v>64.7</v>
       </c>
       <c r="N9" s="1">
         <v>0.34300000000000003</v>
@@ -2981,7 +2994,7 @@
         <v>9.32</v>
       </c>
       <c r="M10" s="7">
-        <v>67.98</v>
+        <v>67.435000000000002</v>
       </c>
       <c r="N10" s="1">
         <v>0.372</v>
@@ -3028,7 +3041,7 @@
         <v>8.32</v>
       </c>
       <c r="M11" s="7">
-        <v>65.12</v>
+        <v>64.905000000000001</v>
       </c>
       <c r="N11" s="1">
         <v>0.38600000000000001</v>
@@ -3075,7 +3088,7 @@
         <v>8.68</v>
       </c>
       <c r="M12" s="7">
-        <v>62.76</v>
+        <v>62.715000000000003</v>
       </c>
       <c r="N12" s="1">
         <v>0.32200000000000001</v>
@@ -3122,7 +3135,7 @@
         <v>6.16</v>
       </c>
       <c r="M13" s="7">
-        <v>68.180000000000007</v>
+        <v>68.504999999999995</v>
       </c>
       <c r="N13" s="1">
         <v>0.378</v>
@@ -3169,7 +3182,7 @@
         <v>5.0599999999999996</v>
       </c>
       <c r="M14" s="7">
-        <v>69.83</v>
+        <v>70.210000000000008</v>
       </c>
       <c r="N14" s="1">
         <v>0.34200000000000003</v>
@@ -3216,7 +3229,7 @@
         <v>11.68</v>
       </c>
       <c r="M15" s="7">
-        <v>63.82</v>
+        <v>63.9</v>
       </c>
       <c r="N15" s="1">
         <v>0.34899999999999998</v>
@@ -3263,7 +3276,7 @@
         <v>10.38</v>
       </c>
       <c r="M16" s="7">
-        <v>64.489999999999995</v>
+        <v>64.149999999999991</v>
       </c>
       <c r="N16" s="1">
         <v>0.33900000000000002</v>
@@ -3289,7 +3302,7 @@
         <v>12.33</v>
       </c>
       <c r="F17" s="6">
-        <v>22788.75</v>
+        <v>22787.9</v>
       </c>
       <c r="G17" s="6">
         <v>7.31</v>
@@ -3310,7 +3323,7 @@
         <v>5.71</v>
       </c>
       <c r="M17" s="7">
-        <v>67.63</v>
+        <v>67.765000000000001</v>
       </c>
       <c r="N17" s="1">
         <v>0.35399999999999998</v>
@@ -3336,7 +3349,7 @@
         <v>10.71</v>
       </c>
       <c r="F18" s="6">
-        <v>24414.66</v>
+        <v>24368.73</v>
       </c>
       <c r="G18" s="6">
         <v>8.52</v>
@@ -3357,7 +3370,7 @@
         <v>9.18</v>
       </c>
       <c r="M18" s="7">
-        <v>68.510000000000005</v>
+        <v>68.66</v>
       </c>
       <c r="N18" s="1">
         <v>0.35899999999999999</v>
@@ -3404,7 +3417,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="M19" s="7">
-        <v>69.86</v>
+        <v>69.414999999999992</v>
       </c>
       <c r="N19" s="1">
         <v>0.32100000000000001</v>
@@ -3451,7 +3464,7 @@
         <v>9.77</v>
       </c>
       <c r="M20" s="7">
-        <v>67.78</v>
+        <v>67.704999999999998</v>
       </c>
       <c r="N20" s="1">
         <v>0.32900000000000001</v>
@@ -3498,7 +3511,7 @@
         <v>10.7</v>
       </c>
       <c r="M21" s="7">
-        <v>61.13</v>
+        <v>60.835000000000001</v>
       </c>
       <c r="N21" s="1">
         <v>0.38800000000000001</v>
@@ -3524,7 +3537,7 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="F22" s="6">
-        <v>166941.5</v>
+        <v>166941.49</v>
       </c>
       <c r="G22" s="6">
         <v>7.78</v>
@@ -3545,7 +3558,7 @@
         <v>11.83</v>
       </c>
       <c r="M22" s="7">
-        <v>64.19</v>
+        <v>63.71</v>
       </c>
       <c r="N22" s="1">
         <v>0.374</v>
@@ -3571,7 +3584,7 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="6">
-        <v>251778.5</v>
+        <v>251778.52</v>
       </c>
       <c r="G23" s="6">
         <v>9.3000000000000007</v>
@@ -3592,7 +3605,7 @@
         <v>10.09</v>
       </c>
       <c r="M23" s="7">
-        <v>65.87</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="N23" s="1">
         <v>0.34</v>
@@ -3639,7 +3652,7 @@
         <v>11.65</v>
       </c>
       <c r="M24" s="7">
-        <v>60.75</v>
+        <v>60.480000000000004</v>
       </c>
       <c r="N24" s="1">
         <v>0.35599999999999998</v>
@@ -3686,7 +3699,7 @@
         <v>3.25</v>
       </c>
       <c r="M25" s="7">
-        <v>74.75</v>
+        <v>74.915000000000006</v>
       </c>
       <c r="N25" s="1">
         <v>0.32</v>
@@ -3733,7 +3746,7 @@
         <v>11.79</v>
       </c>
       <c r="M26" s="7">
-        <v>61.77</v>
+        <v>61.584999999999994</v>
       </c>
       <c r="N26" s="1">
         <v>0.441</v>
@@ -3759,7 +3772,7 @@
         <v>8.25</v>
       </c>
       <c r="F27" s="6">
-        <v>2538923</v>
+        <v>8851.0499999999993</v>
       </c>
       <c r="G27" s="6">
         <v>9.81</v>
@@ -3780,7 +3793,7 @@
         <v>10.78</v>
       </c>
       <c r="M27" s="7">
-        <v>56.86</v>
+        <v>56.724999999999994</v>
       </c>
       <c r="N27" s="1">
         <v>0.436</v>
@@ -3806,7 +3819,7 @@
         <v>4.37</v>
       </c>
       <c r="F28" s="6">
-        <v>200414</v>
+        <v>200414.03</v>
       </c>
       <c r="G28" s="6">
         <v>10.99</v>
@@ -3827,7 +3840,7 @@
         <v>11.46</v>
       </c>
       <c r="M28" s="7">
-        <v>65.31</v>
+        <v>65.22</v>
       </c>
       <c r="N28" s="1">
         <v>0.42699999999999999</v>
@@ -3874,7 +3887,7 @@
         <v>10.53</v>
       </c>
       <c r="M29" s="7">
-        <v>62.87</v>
+        <v>62.97</v>
       </c>
       <c r="N29" s="1">
         <v>0.48899999999999999</v>
@@ -3921,7 +3934,7 @@
         <v>10.88</v>
       </c>
       <c r="M30" s="7">
-        <v>64.760000000000005</v>
+        <v>64.685000000000002</v>
       </c>
       <c r="N30" s="1">
         <v>0.40100000000000002</v>
@@ -3968,7 +3981,7 @@
         <v>9.76</v>
       </c>
       <c r="M31" s="7">
-        <v>62.62</v>
+        <v>62.58</v>
       </c>
       <c r="N31" s="1">
         <v>0.36699999999999999</v>
@@ -4015,7 +4028,7 @@
         <v>13.07</v>
       </c>
       <c r="M32" s="7">
-        <v>61.79</v>
+        <v>61.74</v>
       </c>
       <c r="N32" s="1">
         <v>0.41499999999999998</v>
@@ -4062,7 +4075,7 @@
         <v>7.66</v>
       </c>
       <c r="M33" s="7">
-        <v>65.75</v>
+        <v>65.745000000000005</v>
       </c>
       <c r="N33" s="1">
         <v>0.41399999999999998</v>
@@ -4088,7 +4101,7 @@
         <v>7.11</v>
       </c>
       <c r="F34" s="6">
-        <v>3365.25</v>
+        <v>3371.78</v>
       </c>
       <c r="G34" s="6">
         <v>8.77</v>
@@ -4109,7 +4122,7 @@
         <v>6.09</v>
       </c>
       <c r="M34" s="7">
-        <v>64.069999999999993</v>
+        <v>64.335000000000008</v>
       </c>
       <c r="N34" s="1">
         <v>0.34100000000000003</v>
@@ -4156,7 +4169,7 @@
         <v>7.7</v>
       </c>
       <c r="M35" s="7">
-        <v>62.32</v>
+        <v>61.984999999999999</v>
       </c>
       <c r="N35" s="1">
         <v>0.26600000000000001</v>
@@ -4203,7 +4216,7 @@
         <v>7.86</v>
       </c>
       <c r="M36" s="7">
-        <v>66.75</v>
+        <v>66.39</v>
       </c>
       <c r="N36" s="1">
         <v>0.33200000000000002</v>
@@ -4250,7 +4263,7 @@
         <v>9.06</v>
       </c>
       <c r="M37" s="7">
-        <v>63.94</v>
+        <v>63.54</v>
       </c>
       <c r="N37" s="1">
         <v>0.29399999999999998</v>
@@ -4297,7 +4310,7 @@
         <v>10.58</v>
       </c>
       <c r="M38" s="7">
-        <v>63.86</v>
+        <v>63.725000000000001</v>
       </c>
       <c r="N38" s="1">
         <v>0.26400000000000001</v>
@@ -4323,7 +4336,7 @@
         <v>5.93</v>
       </c>
       <c r="F39" s="6">
-        <v>106413.7</v>
+        <v>106413.71</v>
       </c>
       <c r="G39" s="6">
         <v>10.83</v>
@@ -4344,7 +4357,7 @@
         <v>9.07</v>
       </c>
       <c r="M39" s="7">
-        <v>64.52</v>
+        <v>64.210000000000008</v>
       </c>
       <c r="N39" s="1">
         <v>0.34300000000000003</v>
@@ -4391,7 +4404,7 @@
         <v>10.130000000000001</v>
       </c>
       <c r="M40" s="7">
-        <v>61.37</v>
+        <v>60.980000000000004</v>
       </c>
       <c r="N40" s="1">
         <v>0.36299999999999999</v>
@@ -4438,7 +4451,7 @@
         <v>9.41</v>
       </c>
       <c r="M41" s="7">
-        <v>62.16</v>
+        <v>61.75</v>
       </c>
       <c r="N41" s="1">
         <v>0.34</v>
@@ -4485,7 +4498,7 @@
         <v>8.6</v>
       </c>
       <c r="M42" s="7">
-        <v>62.56</v>
+        <v>62.51</v>
       </c>
       <c r="N42" s="1">
         <v>0.37</v>
@@ -4615,7 +4628,7 @@
         <v>8.4700000000000006</v>
       </c>
       <c r="M2" s="7">
-        <v>67.680000000000007</v>
+        <v>67.72</v>
       </c>
       <c r="N2" s="1">
         <v>0.21099999999999999</v>
@@ -4641,7 +4654,7 @@
         <v>3.52</v>
       </c>
       <c r="F3" s="6">
-        <v>451772.7</v>
+        <v>451772.69</v>
       </c>
       <c r="G3" s="6">
         <v>11.66</v>
@@ -4662,7 +4675,7 @@
         <v>5.63</v>
       </c>
       <c r="M3" s="7">
-        <v>63.07</v>
+        <v>63.284999999999997</v>
       </c>
       <c r="N3" s="1">
         <v>0.377</v>
@@ -4688,7 +4701,7 @@
         <v>4.3</v>
       </c>
       <c r="F4" s="6">
-        <v>329546.3</v>
+        <v>329546.33</v>
       </c>
       <c r="G4" s="6">
         <v>11.73</v>
@@ -4709,7 +4722,7 @@
         <v>8.39</v>
       </c>
       <c r="M4" s="7">
-        <v>61.26</v>
+        <v>61.47</v>
       </c>
       <c r="N4" s="1">
         <v>0.374</v>
@@ -4735,7 +4748,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F5" s="6">
-        <v>481954.5</v>
+        <v>481954.45</v>
       </c>
       <c r="G5" s="6">
         <v>11.53</v>
@@ -4756,7 +4769,7 @@
         <v>5.88</v>
       </c>
       <c r="M5" s="7">
-        <v>63.6</v>
+        <v>63.815000000000005</v>
       </c>
       <c r="N5" s="1">
         <v>0.34300000000000003</v>
@@ -4782,7 +4795,7 @@
         <v>4.22</v>
       </c>
       <c r="F6" s="6">
-        <v>345619.6</v>
+        <v>345619.56</v>
       </c>
       <c r="G6" s="6">
         <v>11.13</v>
@@ -4803,7 +4816,7 @@
         <v>7.1</v>
       </c>
       <c r="M6" s="7">
-        <v>63.97</v>
+        <v>64.125</v>
       </c>
       <c r="N6" s="1">
         <v>0.42199999999999999</v>
@@ -4829,7 +4842,7 @@
         <v>7.24</v>
       </c>
       <c r="F7" s="6">
-        <v>350233.7</v>
+        <v>350233.72</v>
       </c>
       <c r="G7" s="6">
         <v>10.82</v>
@@ -4850,7 +4863,7 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="M7" s="7">
-        <v>64.34</v>
+        <v>64.805000000000007</v>
       </c>
       <c r="N7" s="1">
         <v>0.54300000000000004</v>
@@ -4876,7 +4889,7 @@
         <v>7.73</v>
       </c>
       <c r="F8" s="6">
-        <v>167966.2</v>
+        <v>167966.18</v>
       </c>
       <c r="G8" s="6">
         <v>8.34</v>
@@ -4897,7 +4910,7 @@
         <v>10.64</v>
       </c>
       <c r="M8" s="7">
-        <v>63.75</v>
+        <v>63.2</v>
       </c>
       <c r="N8" s="1">
         <v>0.4</v>
@@ -4944,7 +4957,7 @@
         <v>7.77</v>
       </c>
       <c r="M9" s="7">
-        <v>69.11</v>
+        <v>68.92</v>
       </c>
       <c r="N9" s="1">
         <v>0.309</v>
@@ -4991,7 +5004,7 @@
         <v>8.41</v>
       </c>
       <c r="M10" s="7">
-        <v>69.98</v>
+        <v>69.484999999999999</v>
       </c>
       <c r="N10" s="1">
         <v>0.313</v>
@@ -5038,7 +5051,7 @@
         <v>6.98</v>
       </c>
       <c r="M11" s="7">
-        <v>63.64</v>
+        <v>63.435000000000002</v>
       </c>
       <c r="N11" s="1">
         <v>0.37</v>
@@ -5085,7 +5098,7 @@
         <v>7.6</v>
       </c>
       <c r="M12" s="7">
-        <v>68.84</v>
+        <v>68.81</v>
       </c>
       <c r="N12" s="1">
         <v>0.30199999999999999</v>
@@ -5132,7 +5145,7 @@
         <v>4.17</v>
       </c>
       <c r="M13" s="7">
-        <v>67.83</v>
+        <v>68.135000000000005</v>
       </c>
       <c r="N13" s="1">
         <v>0.378</v>
@@ -5179,7 +5192,7 @@
         <v>3.75</v>
       </c>
       <c r="M14" s="7">
-        <v>68.47</v>
+        <v>68.86</v>
       </c>
       <c r="N14" s="1">
         <v>0.33700000000000002</v>
@@ -5226,7 +5239,7 @@
         <v>9.81</v>
       </c>
       <c r="M15" s="7">
-        <v>61.8</v>
+        <v>61.884999999999998</v>
       </c>
       <c r="N15" s="1">
         <v>0.34499999999999997</v>
@@ -5273,7 +5286,7 @@
         <v>8.11</v>
       </c>
       <c r="M16" s="7">
-        <v>65.53</v>
+        <v>65.164999999999992</v>
       </c>
       <c r="N16" s="1">
         <v>0.35499999999999998</v>
@@ -5320,7 +5333,7 @@
         <v>4.16</v>
       </c>
       <c r="M17" s="7">
-        <v>66.209999999999994</v>
+        <v>66.38</v>
       </c>
       <c r="N17" s="1">
         <v>0.36699999999999999</v>
@@ -5367,7 +5380,7 @@
         <v>7.72</v>
       </c>
       <c r="M18" s="7">
-        <v>64.63</v>
+        <v>64.84</v>
       </c>
       <c r="N18" s="1">
         <v>0.39400000000000002</v>
@@ -5414,7 +5427,7 @@
         <v>6.49</v>
       </c>
       <c r="M19" s="7">
-        <v>69.08</v>
+        <v>68.644999999999996</v>
       </c>
       <c r="N19" s="1">
         <v>0.3</v>
@@ -5461,7 +5474,7 @@
         <v>7.77</v>
       </c>
       <c r="M20" s="7">
-        <v>68.87</v>
+        <v>68.8</v>
       </c>
       <c r="N20" s="1">
         <v>0.36</v>
@@ -5508,7 +5521,7 @@
         <v>8.75</v>
       </c>
       <c r="M21" s="7">
-        <v>65.209999999999994</v>
+        <v>64.915000000000006</v>
       </c>
       <c r="N21" s="1">
         <v>0.36699999999999999</v>
@@ -5534,7 +5547,7 @@
         <v>8.44</v>
       </c>
       <c r="F22" s="6">
-        <v>177470.9</v>
+        <v>177470.89</v>
       </c>
       <c r="G22" s="6">
         <v>7.96</v>
@@ -5555,7 +5568,7 @@
         <v>9.8699999999999992</v>
       </c>
       <c r="M22" s="7">
-        <v>65.510000000000005</v>
+        <v>65.02</v>
       </c>
       <c r="N22" s="1">
         <v>0.35299999999999998</v>
@@ -5581,7 +5594,7 @@
         <v>5.01</v>
       </c>
       <c r="F23" s="6">
-        <v>265120.5</v>
+        <v>265120.49</v>
       </c>
       <c r="G23" s="6">
         <v>9.5299999999999994</v>
@@ -5602,7 +5615,7 @@
         <v>10.31</v>
       </c>
       <c r="M23" s="7">
-        <v>65.41</v>
+        <v>65.06</v>
       </c>
       <c r="N23" s="1">
         <v>0.373</v>
@@ -5649,7 +5662,7 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="M24" s="7">
-        <v>64.37</v>
+        <v>64.094999999999999</v>
       </c>
       <c r="N24" s="1">
         <v>0.36799999999999999</v>
@@ -5675,7 +5688,7 @@
         <v>9.32</v>
       </c>
       <c r="F25" s="6">
-        <v>2383665</v>
+        <v>8426.4</v>
       </c>
       <c r="G25" s="5">
         <v>8.0299999999999994</v>
@@ -5696,7 +5709,7 @@
         <v>1.56</v>
       </c>
       <c r="M25" s="7">
-        <v>79.92</v>
+        <v>80.034999999999997</v>
       </c>
       <c r="N25" s="1">
         <v>0.29399999999999998</v>
@@ -5743,7 +5756,7 @@
         <v>10.78</v>
       </c>
       <c r="M26" s="7">
-        <v>64.209999999999994</v>
+        <v>64.03</v>
       </c>
       <c r="N26" s="1">
         <v>0.43</v>
@@ -5790,7 +5803,7 @@
         <v>8.83</v>
       </c>
       <c r="M27" s="7">
-        <v>62.48</v>
+        <v>62.33</v>
       </c>
       <c r="N27" s="1">
         <v>0.48199999999999998</v>
@@ -5816,7 +5829,7 @@
         <v>4.25</v>
       </c>
       <c r="F28" s="6">
-        <v>211250.7</v>
+        <v>211250.67</v>
       </c>
       <c r="G28" s="5">
         <v>11</v>
@@ -5837,7 +5850,7 @@
         <v>9.5500000000000007</v>
       </c>
       <c r="M28" s="7">
-        <v>69.42</v>
+        <v>69.33</v>
       </c>
       <c r="N28" s="1">
         <v>0.45900000000000002</v>
@@ -5884,7 +5897,7 @@
         <v>8.42</v>
       </c>
       <c r="M29" s="7">
-        <v>65.42</v>
+        <v>65.539999999999992</v>
       </c>
       <c r="N29" s="1">
         <v>0.46800000000000003</v>
@@ -5931,7 +5944,7 @@
         <v>8.81</v>
       </c>
       <c r="M30" s="7">
-        <v>65.33</v>
+        <v>65.254999999999995</v>
       </c>
       <c r="N30" s="1">
         <v>0.441</v>
@@ -5978,7 +5991,7 @@
         <v>7.82</v>
       </c>
       <c r="M31" s="7">
-        <v>63.35</v>
+        <v>63.31</v>
       </c>
       <c r="N31" s="1">
         <v>0.39400000000000002</v>
@@ -6025,7 +6038,7 @@
         <v>10.77</v>
       </c>
       <c r="M32" s="7">
-        <v>67.22</v>
+        <v>67.16</v>
       </c>
       <c r="N32" s="1">
         <v>0.40799999999999997</v>
@@ -6072,7 +6085,7 @@
         <v>6.62</v>
       </c>
       <c r="M33" s="7">
-        <v>65.989999999999995</v>
+        <v>65.984999999999999</v>
       </c>
       <c r="N33" s="1">
         <v>0.40500000000000003</v>
@@ -6119,7 +6132,7 @@
         <v>5.53</v>
       </c>
       <c r="M34" s="7">
-        <v>63.76</v>
+        <v>64.13</v>
       </c>
       <c r="N34" s="1">
         <v>0.36199999999999999</v>
@@ -6166,7 +6179,7 @@
         <v>9.24</v>
       </c>
       <c r="M35" s="7">
-        <v>61.66</v>
+        <v>61.324999999999996</v>
       </c>
       <c r="N35" s="1">
         <v>0.30199999999999999</v>
@@ -6213,7 +6226,7 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="M36" s="7">
-        <v>66.17</v>
+        <v>65.814999999999998</v>
       </c>
       <c r="N36" s="1">
         <v>0.312</v>
@@ -6239,7 +6252,7 @@
         <v>6.92</v>
       </c>
       <c r="F37" s="6">
-        <v>103219.4</v>
+        <v>103219.44</v>
       </c>
       <c r="G37" s="6">
         <v>8.92</v>
@@ -6260,7 +6273,7 @@
         <v>7.88</v>
       </c>
       <c r="M37" s="7">
-        <v>67.05</v>
+        <v>66.694999999999993</v>
       </c>
       <c r="N37" s="1">
         <v>0.28199999999999997</v>
@@ -6307,7 +6320,7 @@
         <v>10.61</v>
       </c>
       <c r="M38" s="7">
-        <v>64.25</v>
+        <v>64.135000000000005</v>
       </c>
       <c r="N38" s="1">
         <v>0.28399999999999997</v>
@@ -6354,7 +6367,7 @@
         <v>7.16</v>
       </c>
       <c r="M39" s="7">
-        <v>66.08</v>
+        <v>65.734999999999999</v>
       </c>
       <c r="N39" s="1">
         <v>0.38300000000000001</v>
@@ -6401,7 +6414,7 @@
         <v>8.1</v>
       </c>
       <c r="M40" s="7">
-        <v>67.39</v>
+        <v>66.990000000000009</v>
       </c>
       <c r="N40" s="1">
         <v>0.318</v>
@@ -6448,7 +6461,7 @@
         <v>8.17</v>
       </c>
       <c r="M41" s="7">
-        <v>64.8</v>
+        <v>64.45</v>
       </c>
       <c r="N41" s="1">
         <v>0.35399999999999998</v>
@@ -6495,7 +6508,7 @@
         <v>6.59</v>
       </c>
       <c r="M42" s="7">
-        <v>58.67</v>
+        <v>58.625</v>
       </c>
       <c r="N42" s="1">
         <v>0.35899999999999999</v>
@@ -6625,7 +6638,7 @@
         <v>8.11</v>
       </c>
       <c r="M2" s="7">
-        <v>73.7</v>
+        <v>73.724999999999994</v>
       </c>
       <c r="N2" s="1">
         <v>0.43</v>
@@ -6672,7 +6685,7 @@
         <v>5.37</v>
       </c>
       <c r="M3" s="7">
-        <v>66.05</v>
+        <v>66.054999999999993</v>
       </c>
       <c r="N3" s="1">
         <v>0.43</v>
@@ -6698,7 +6711,7 @@
         <v>4.2</v>
       </c>
       <c r="F4" s="6">
-        <v>346508.7</v>
+        <v>346508.69</v>
       </c>
       <c r="G4" s="6">
         <v>11.88</v>
@@ -6719,7 +6732,7 @@
         <v>7.24</v>
       </c>
       <c r="M4" s="7">
-        <v>65.11</v>
+        <v>65.14</v>
       </c>
       <c r="N4" s="1">
         <v>0.43</v>
@@ -6745,7 +6758,7 @@
         <v>4.68</v>
       </c>
       <c r="F5" s="6">
-        <v>506560.7</v>
+        <v>506560.74</v>
       </c>
       <c r="G5" s="6">
         <v>11.54</v>
@@ -6766,7 +6779,7 @@
         <v>6.42</v>
       </c>
       <c r="M5" s="7">
-        <v>63.98</v>
+        <v>63.825000000000003</v>
       </c>
       <c r="N5" s="1">
         <v>0.43</v>
@@ -6792,7 +6805,7 @@
         <v>4.09</v>
       </c>
       <c r="F6" s="6">
-        <v>363931.2</v>
+        <v>363931.23</v>
       </c>
       <c r="G6" s="6">
         <v>11.23</v>
@@ -6813,7 +6826,7 @@
         <v>6.39</v>
       </c>
       <c r="M6" s="7">
-        <v>64.8</v>
+        <v>64.765000000000001</v>
       </c>
       <c r="N6" s="1">
         <v>0.43</v>
@@ -6839,7 +6852,7 @@
         <v>6.78</v>
       </c>
       <c r="F7" s="6">
-        <v>364823.9</v>
+        <v>364823.88</v>
       </c>
       <c r="G7" s="6">
         <v>10.84</v>
@@ -6860,7 +6873,7 @@
         <v>7.05</v>
       </c>
       <c r="M7" s="7">
-        <v>65.5</v>
+        <v>65.425000000000011</v>
       </c>
       <c r="N7" s="1">
         <v>0.43</v>
@@ -6886,7 +6899,7 @@
         <v>7.27</v>
       </c>
       <c r="F8" s="6">
-        <v>176683.6</v>
+        <v>176683.58</v>
       </c>
       <c r="G8" s="6">
         <v>8.3699999999999992</v>
@@ -6907,7 +6920,7 @@
         <v>8.4700000000000006</v>
       </c>
       <c r="M8" s="7">
-        <v>64.22</v>
+        <v>63.65</v>
       </c>
       <c r="N8" s="1">
         <v>0.36899999999999999</v>
@@ -6954,7 +6967,7 @@
         <v>7.32</v>
       </c>
       <c r="M9" s="7">
-        <v>67.75</v>
+        <v>67.510000000000005</v>
       </c>
       <c r="N9" s="1">
         <v>0.35499999999999998</v>
@@ -7001,7 +7014,7 @@
         <v>7.71</v>
       </c>
       <c r="M10" s="7">
-        <v>72.31</v>
+        <v>71.875</v>
       </c>
       <c r="N10" s="1">
         <v>0.31900000000000001</v>
@@ -7048,7 +7061,7 @@
         <v>6.52</v>
       </c>
       <c r="M11" s="7">
-        <v>67.099999999999994</v>
+        <v>66.814999999999998</v>
       </c>
       <c r="N11" s="1">
         <v>0.34799999999999998</v>
@@ -7095,7 +7108,7 @@
         <v>7.33</v>
       </c>
       <c r="M12" s="7">
-        <v>70.099999999999994</v>
+        <v>69.745000000000005</v>
       </c>
       <c r="N12" s="1">
         <v>0.36099999999999999</v>
@@ -7142,7 +7155,7 @@
         <v>3.89</v>
       </c>
       <c r="M13" s="7">
-        <v>68.37</v>
+        <v>68.215000000000003</v>
       </c>
       <c r="N13" s="1">
         <v>0.40400000000000003</v>
@@ -7189,7 +7202,7 @@
         <v>3.52</v>
       </c>
       <c r="M14" s="7">
-        <v>66.260000000000005</v>
+        <v>66.35499999999999</v>
       </c>
       <c r="N14" s="1">
         <v>0.34100000000000003</v>
@@ -7236,7 +7249,7 @@
         <v>9.49</v>
       </c>
       <c r="M15" s="7">
-        <v>61.95</v>
+        <v>61.775000000000006</v>
       </c>
       <c r="N15" s="1">
         <v>0.35099999999999998</v>
@@ -7283,7 +7296,7 @@
         <v>7.65</v>
       </c>
       <c r="M16" s="7">
-        <v>66.16</v>
+        <v>66.009999999999991</v>
       </c>
       <c r="N16" s="1">
         <v>0.36099999999999999</v>
@@ -7330,7 +7343,7 @@
         <v>4.12</v>
       </c>
       <c r="M17" s="7">
-        <v>68.5</v>
+        <v>68.534999999999997</v>
       </c>
       <c r="N17" s="1">
         <v>0.34200000000000003</v>
@@ -7377,7 +7390,7 @@
         <v>6.94</v>
       </c>
       <c r="M18" s="7">
-        <v>67.760000000000005</v>
+        <v>67.694999999999993</v>
       </c>
       <c r="N18" s="1">
         <v>0.36599999999999999</v>
@@ -7424,7 +7437,7 @@
         <v>6.46</v>
       </c>
       <c r="M19" s="7">
-        <v>63.88</v>
+        <v>63.9</v>
       </c>
       <c r="N19" s="1">
         <v>0.34399999999999997</v>
@@ -7471,7 +7484,7 @@
         <v>7.65</v>
       </c>
       <c r="M20" s="7">
-        <v>70.03</v>
+        <v>70.105000000000004</v>
       </c>
       <c r="N20" s="1">
         <v>0.33100000000000002</v>
@@ -7518,7 +7531,7 @@
         <v>7.72</v>
       </c>
       <c r="M21" s="7">
-        <v>66.37</v>
+        <v>66.150000000000006</v>
       </c>
       <c r="N21" s="1">
         <v>0.372</v>
@@ -7544,7 +7557,7 @@
         <v>7.87</v>
       </c>
       <c r="F22" s="6">
-        <v>187051.7</v>
+        <v>187051.65</v>
       </c>
       <c r="G22" s="5">
         <v>8.0399999999999991</v>
@@ -7565,7 +7578,7 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="M22" s="7">
-        <v>63.4</v>
+        <v>63.225000000000001</v>
       </c>
       <c r="N22" s="1">
         <v>0.38900000000000001</v>
@@ -7612,7 +7625,7 @@
         <v>8.8699999999999992</v>
       </c>
       <c r="M23" s="7">
-        <v>65</v>
+        <v>64.78</v>
       </c>
       <c r="N23" s="1">
         <v>0.39700000000000002</v>
@@ -7659,7 +7672,7 @@
         <v>8.11</v>
       </c>
       <c r="M24" s="7">
-        <v>67.010000000000005</v>
+        <v>66.634999999999991</v>
       </c>
       <c r="N24" s="1">
         <v>0.374</v>
@@ -7706,7 +7719,7 @@
         <v>1.52</v>
       </c>
       <c r="M25" s="7">
-        <v>80.150000000000006</v>
+        <v>80.215000000000003</v>
       </c>
       <c r="N25" s="1">
         <v>0.32300000000000001</v>
@@ -7753,7 +7766,7 @@
         <v>9.39</v>
       </c>
       <c r="M26" s="7">
-        <v>64.81</v>
+        <v>64.635000000000005</v>
       </c>
       <c r="N26" s="1">
         <v>0.46400000000000002</v>
@@ -7800,7 +7813,7 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="M27" s="7">
-        <v>62.57</v>
+        <v>62.589999999999996</v>
       </c>
       <c r="N27" s="1">
         <v>0.45800000000000002</v>
@@ -7826,7 +7839,7 @@
         <v>3.96</v>
       </c>
       <c r="F28" s="6">
-        <v>221969.1</v>
+        <v>221969.13</v>
       </c>
       <c r="G28" s="5">
         <v>11.06</v>
@@ -7847,7 +7860,7 @@
         <v>8.83</v>
       </c>
       <c r="M28" s="7">
-        <v>66.97</v>
+        <v>66.974999999999994</v>
       </c>
       <c r="N28" s="1">
         <v>0.45900000000000002</v>
@@ -7894,7 +7907,7 @@
         <v>7.66</v>
       </c>
       <c r="M29" s="7">
-        <v>68.709999999999994</v>
+        <v>68.745000000000005</v>
       </c>
       <c r="N29" s="1">
         <v>0.46800000000000003</v>
@@ -7941,7 +7954,7 @@
         <v>7.9</v>
       </c>
       <c r="M30" s="7">
-        <v>64.650000000000006</v>
+        <v>64.644999999999996</v>
       </c>
       <c r="N30" s="1">
         <v>0.41399999999999998</v>
@@ -7988,7 +8001,7 @@
         <v>6.97</v>
       </c>
       <c r="M31" s="7">
-        <v>62.76</v>
+        <v>62.724999999999994</v>
       </c>
       <c r="N31" s="1">
         <v>0.40200000000000002</v>
@@ -8035,7 +8048,7 @@
         <v>10.52</v>
       </c>
       <c r="M32" s="7">
-        <v>68.430000000000007</v>
+        <v>68.36</v>
       </c>
       <c r="N32" s="1">
         <v>0.39400000000000002</v>
@@ -8082,7 +8095,7 @@
         <v>6.55</v>
       </c>
       <c r="M33" s="7">
-        <v>65.44</v>
+        <v>65.284999999999997</v>
       </c>
       <c r="N33" s="1">
         <v>0.42799999999999999</v>
@@ -8129,7 +8142,7 @@
         <v>5.43</v>
       </c>
       <c r="M34" s="7">
-        <v>67.44</v>
+        <v>67.474999999999994</v>
       </c>
       <c r="N34" s="1">
         <v>0.33700000000000002</v>
@@ -8176,7 +8189,7 @@
         <v>9.0500000000000007</v>
       </c>
       <c r="M35" s="7">
-        <v>60.33</v>
+        <v>59.85</v>
       </c>
       <c r="N35" s="1">
         <v>0.24299999999999999</v>
@@ -8223,7 +8236,7 @@
         <v>7.57</v>
       </c>
       <c r="M36" s="7">
-        <v>67.900000000000006</v>
+        <v>67.39500000000001</v>
       </c>
       <c r="N36" s="1">
         <v>0.27100000000000002</v>
@@ -8249,7 +8262,7 @@
         <v>6.93</v>
       </c>
       <c r="F37" s="6">
-        <v>108569.8</v>
+        <v>108569.83</v>
       </c>
       <c r="G37" s="6">
         <v>8.93</v>
@@ -8270,7 +8283,7 @@
         <v>6.94</v>
       </c>
       <c r="M37" s="7">
-        <v>66.87</v>
+        <v>66.524999999999991</v>
       </c>
       <c r="N37" s="1">
         <v>0.28599999999999998</v>
@@ -8317,7 +8330,7 @@
         <v>9.94</v>
       </c>
       <c r="M38" s="7">
-        <v>63.22</v>
+        <v>62.834999999999994</v>
       </c>
       <c r="N38" s="1">
         <v>0.27400000000000002</v>
@@ -8343,7 +8356,7 @@
         <v>5.89</v>
       </c>
       <c r="F39" s="6">
-        <v>119059.9</v>
+        <v>119059.85</v>
       </c>
       <c r="G39" s="6">
         <v>10.91</v>
@@ -8364,7 +8377,7 @@
         <v>6.76</v>
       </c>
       <c r="M39" s="7">
-        <v>63.39</v>
+        <v>63.31</v>
       </c>
       <c r="N39" s="1">
         <v>0.379</v>
@@ -8411,7 +8424,7 @@
         <v>7.25</v>
       </c>
       <c r="M40" s="7">
-        <v>62.7</v>
+        <v>62.49</v>
       </c>
       <c r="N40" s="1">
         <v>0.36199999999999999</v>
@@ -8458,7 +8471,7 @@
         <v>7.45</v>
       </c>
       <c r="M41" s="7">
-        <v>68.44</v>
+        <v>68.105000000000004</v>
       </c>
       <c r="N41" s="1">
         <v>0.30599999999999999</v>
@@ -8505,7 +8518,7 @@
         <v>5.81</v>
       </c>
       <c r="M42" s="7">
-        <v>60.5</v>
+        <v>60.655000000000001</v>
       </c>
       <c r="N42" s="1">
         <v>0.35899999999999999</v>
@@ -8635,7 +8648,7 @@
         <v>7.93</v>
       </c>
       <c r="M2" s="8">
-        <v>72.58</v>
+        <v>72.664999999999992</v>
       </c>
       <c r="N2" s="1">
         <v>0.42699999999999999</v>
@@ -8661,7 +8674,7 @@
         <v>3.03</v>
       </c>
       <c r="F3" s="6">
-        <v>500422.7</v>
+        <v>500422.68</v>
       </c>
       <c r="G3" s="6">
         <v>11.95</v>
@@ -8682,7 +8695,7 @@
         <v>5.22</v>
       </c>
       <c r="M3" s="7">
-        <v>64.81</v>
+        <v>64.835000000000008</v>
       </c>
       <c r="N3" s="1">
         <v>0.42699999999999999</v>
@@ -8708,7 +8721,7 @@
         <v>4.09</v>
       </c>
       <c r="F4" s="6">
-        <v>362068.1</v>
+        <v>362068.12</v>
       </c>
       <c r="G4" s="6">
         <v>11.99</v>
@@ -8729,7 +8742,7 @@
         <v>6.95</v>
       </c>
       <c r="M4" s="7">
-        <v>64.489999999999995</v>
+        <v>64.545000000000002</v>
       </c>
       <c r="N4" s="1">
         <v>0.42699999999999999</v>
@@ -8755,7 +8768,7 @@
         <v>4.63</v>
       </c>
       <c r="F5" s="6">
-        <v>532606.9</v>
+        <v>532606.87</v>
       </c>
       <c r="G5" s="6">
         <v>11.61</v>
@@ -8776,7 +8789,7 @@
         <v>6.24</v>
       </c>
       <c r="M5" s="7">
-        <v>65.12</v>
+        <v>64.965000000000003</v>
       </c>
       <c r="N5" s="1">
         <v>0.42699999999999999</v>
@@ -8802,7 +8815,7 @@
         <v>3.94</v>
       </c>
       <c r="F6" s="6">
-        <v>383113.1</v>
+        <v>383113.08</v>
       </c>
       <c r="G6" s="6">
         <v>11.24</v>
@@ -8823,7 +8836,7 @@
         <v>6.18</v>
       </c>
       <c r="M6" s="7">
-        <v>64.12</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="N6" s="1">
         <v>0.42699999999999999</v>
@@ -8849,7 +8862,7 @@
         <v>6.44</v>
       </c>
       <c r="F7" s="6">
-        <v>380461.1</v>
+        <v>380461.09</v>
       </c>
       <c r="G7" s="6">
         <v>10.85</v>
@@ -8870,7 +8883,7 @@
         <v>6.18</v>
       </c>
       <c r="M7" s="8">
-        <v>67.77</v>
+        <v>67.72</v>
       </c>
       <c r="N7" s="1">
         <v>0.42699999999999999</v>
@@ -8896,7 +8909,7 @@
         <v>7.05</v>
       </c>
       <c r="F8" s="6">
-        <v>185882.3</v>
+        <v>185882.34</v>
       </c>
       <c r="G8" s="6">
         <v>8.39</v>
@@ -8917,7 +8930,7 @@
         <v>7.34</v>
       </c>
       <c r="M8" s="7">
-        <v>66.3</v>
+        <v>65.78</v>
       </c>
       <c r="N8" s="1">
         <v>0.39800000000000002</v>
@@ -8964,7 +8977,7 @@
         <v>7.11</v>
       </c>
       <c r="M9" s="7">
-        <v>69.75</v>
+        <v>69.564999999999998</v>
       </c>
       <c r="N9" s="1">
         <v>0.34200000000000003</v>
@@ -9011,7 +9024,7 @@
         <v>5.99</v>
       </c>
       <c r="M10" s="7">
-        <v>72.63</v>
+        <v>72.234999999999999</v>
       </c>
       <c r="N10" s="1">
         <v>0.33800000000000002</v>
@@ -9058,7 +9071,7 @@
         <v>6.36</v>
       </c>
       <c r="M11" s="7">
-        <v>67.22</v>
+        <v>66.97999999999999</v>
       </c>
       <c r="N11" s="1">
         <v>0.36399999999999999</v>
@@ -9105,7 +9118,7 @@
         <v>6.96</v>
       </c>
       <c r="M12" s="7">
-        <v>71.34</v>
+        <v>71.010000000000005</v>
       </c>
       <c r="N12" s="1">
         <v>0.32400000000000001</v>
@@ -9152,7 +9165,7 @@
         <v>3.74</v>
       </c>
       <c r="M13" s="7">
-        <v>68.760000000000005</v>
+        <v>68.62</v>
       </c>
       <c r="N13" s="1">
         <v>0.36299999999999999</v>
@@ -9199,7 +9212,7 @@
         <v>3.37</v>
       </c>
       <c r="M14" s="7">
-        <v>68.14</v>
+        <v>68.22</v>
       </c>
       <c r="N14" s="1">
         <v>0.32600000000000001</v>
@@ -9246,7 +9259,7 @@
         <v>7.78</v>
       </c>
       <c r="M15" s="7">
-        <v>65.84</v>
+        <v>65.709999999999994</v>
       </c>
       <c r="N15" s="1">
         <v>0.36899999999999999</v>
@@ -9293,7 +9306,7 @@
         <v>6.74</v>
       </c>
       <c r="M16" s="7">
-        <v>69.27</v>
+        <v>69.16</v>
       </c>
       <c r="N16" s="1">
         <v>0.374</v>
@@ -9340,7 +9353,7 @@
         <v>4.01</v>
       </c>
       <c r="M17" s="7">
-        <v>69.64</v>
+        <v>69.674999999999997</v>
       </c>
       <c r="N17" s="1">
         <v>0.35399999999999998</v>
@@ -9387,7 +9400,7 @@
         <v>6.16</v>
       </c>
       <c r="M18" s="7">
-        <v>69.239999999999995</v>
+        <v>69.194999999999993</v>
       </c>
       <c r="N18" s="1">
         <v>0.33700000000000002</v>
@@ -9434,7 +9447,7 @@
         <v>6.25</v>
       </c>
       <c r="M19" s="7">
-        <v>66.430000000000007</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="N19" s="1">
         <v>0.30599999999999999</v>
@@ -9481,7 +9494,7 @@
         <v>6.73</v>
       </c>
       <c r="M20" s="7">
-        <v>71.709999999999994</v>
+        <v>71.795000000000002</v>
       </c>
       <c r="N20" s="1">
         <v>0.32</v>
@@ -9528,7 +9541,7 @@
         <v>7.34</v>
       </c>
       <c r="M21" s="7">
-        <v>66.62</v>
+        <v>66.405000000000001</v>
       </c>
       <c r="N21" s="1">
         <v>0.39800000000000002</v>
@@ -9575,7 +9588,7 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="M22" s="7">
-        <v>63.67</v>
+        <v>63.519999999999996</v>
       </c>
       <c r="N22" s="1">
         <v>0.376</v>
@@ -9601,7 +9614,7 @@
         <v>4.8</v>
       </c>
       <c r="F23" s="6">
-        <v>293664.8</v>
+        <v>293664.78999999998</v>
       </c>
       <c r="G23" s="6">
         <v>9.76</v>
@@ -9622,7 +9635,7 @@
         <v>8.82</v>
       </c>
       <c r="M23" s="7">
-        <v>65.11</v>
+        <v>64.925000000000011</v>
       </c>
       <c r="N23" s="1">
         <v>0.36699999999999999</v>
@@ -9669,7 +9682,7 @@
         <v>6.7</v>
       </c>
       <c r="M24" s="7">
-        <v>68.3</v>
+        <v>67.98</v>
       </c>
       <c r="N24" s="1">
         <v>0.4</v>
@@ -9716,7 +9729,7 @@
         <v>1.58</v>
       </c>
       <c r="M25" s="7">
-        <v>80.12</v>
+        <v>80.210000000000008</v>
       </c>
       <c r="N25" s="1">
         <v>0.28599999999999998</v>
@@ -9763,7 +9776,7 @@
         <v>8.1300000000000008</v>
       </c>
       <c r="M26" s="7">
-        <v>67.349999999999994</v>
+        <v>67.199999999999989</v>
       </c>
       <c r="N26" s="1">
         <v>0.47699999999999998</v>
@@ -9810,7 +9823,7 @@
         <v>8.34</v>
       </c>
       <c r="M27" s="7">
-        <v>62.58</v>
+        <v>62.605000000000004</v>
       </c>
       <c r="N27" s="1">
         <v>0.436</v>
@@ -9836,7 +9849,7 @@
         <v>3.87</v>
       </c>
       <c r="F28" s="6">
-        <v>233053.8</v>
+        <v>233053.79</v>
       </c>
       <c r="G28" s="5">
         <v>11.07</v>
@@ -9857,7 +9870,7 @@
         <v>7.4</v>
       </c>
       <c r="M28" s="7">
-        <v>67.930000000000007</v>
+        <v>67.945000000000007</v>
       </c>
       <c r="N28" s="1">
         <v>0.44</v>
@@ -9904,7 +9917,7 @@
         <v>6.29</v>
       </c>
       <c r="M29" s="7">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="N29" s="1">
         <v>0.42399999999999999</v>
@@ -9951,7 +9964,7 @@
         <v>7.82</v>
       </c>
       <c r="M30" s="7">
-        <v>65.58</v>
+        <v>65.585000000000008</v>
       </c>
       <c r="N30" s="1">
         <v>0.435</v>
@@ -9998,7 +10011,7 @@
         <v>6.27</v>
       </c>
       <c r="M31" s="7">
-        <v>62.89</v>
+        <v>62.865000000000002</v>
       </c>
       <c r="N31" s="1">
         <v>0.39800000000000002</v>
@@ -10045,7 +10058,7 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="M32" s="7">
-        <v>66.52</v>
+        <v>66.445000000000007</v>
       </c>
       <c r="N32" s="1">
         <v>0.40200000000000002</v>
@@ -10092,7 +10105,7 @@
         <v>6.49</v>
       </c>
       <c r="M33" s="7">
-        <v>68.92</v>
+        <v>68.784999999999997</v>
       </c>
       <c r="N33" s="1">
         <v>0.35899999999999999</v>
@@ -10139,7 +10152,7 @@
         <v>5.44</v>
       </c>
       <c r="M34" s="7">
-        <v>67.22</v>
+        <v>67.254999999999995</v>
       </c>
       <c r="N34" s="1">
         <v>0.318</v>
@@ -10186,7 +10199,7 @@
         <v>8.09</v>
       </c>
       <c r="M35" s="7">
-        <v>66.92</v>
+        <v>66.47</v>
       </c>
       <c r="N35" s="1">
         <v>0.245</v>
@@ -10233,7 +10246,7 @@
         <v>6.23</v>
       </c>
       <c r="M36" s="7">
-        <v>72.819999999999993</v>
+        <v>72.39500000000001</v>
       </c>
       <c r="N36" s="1">
         <v>0.25700000000000001</v>
@@ -10259,7 +10272,7 @@
         <v>6.55</v>
       </c>
       <c r="F37" s="6">
-        <v>113998.2</v>
+        <v>113998.21</v>
       </c>
       <c r="G37" s="5">
         <v>9.06</v>
@@ -10280,7 +10293,7 @@
         <v>6.06</v>
       </c>
       <c r="M37" s="7">
-        <v>65.88</v>
+        <v>65.534999999999997</v>
       </c>
       <c r="N37" s="1">
         <v>0.26900000000000002</v>
@@ -10327,7 +10340,7 @@
         <v>9.18</v>
       </c>
       <c r="M38" s="7">
-        <v>67.77</v>
+        <v>67.454999999999998</v>
       </c>
       <c r="N38" s="1">
         <v>0.26700000000000002</v>
@@ -10353,7 +10366,7 @@
         <v>5.43</v>
       </c>
       <c r="F39" s="6">
-        <v>125060.3</v>
+        <v>125060.32</v>
       </c>
       <c r="G39" s="6">
         <v>11.14</v>
@@ -10374,7 +10387,7 @@
         <v>5.92</v>
       </c>
       <c r="M39" s="7">
-        <v>66.02</v>
+        <v>65.959999999999994</v>
       </c>
       <c r="N39" s="1">
         <v>0.32500000000000001</v>
@@ -10421,7 +10434,7 @@
         <v>6.08</v>
       </c>
       <c r="M40" s="7">
-        <v>60.83</v>
+        <v>60.66</v>
       </c>
       <c r="N40" s="1">
         <v>0.36</v>
@@ -10468,7 +10481,7 @@
         <v>7.12</v>
       </c>
       <c r="M41" s="7">
-        <v>69.099999999999994</v>
+        <v>68.795000000000002</v>
       </c>
       <c r="N41" s="1">
         <v>0.32400000000000001</v>
@@ -10515,7 +10528,7 @@
         <v>5.09</v>
       </c>
       <c r="M42" s="7">
-        <v>58.13</v>
+        <v>58.295000000000002</v>
       </c>
       <c r="N42" s="1">
         <v>0.39500000000000002</v>
